--- a/reports/一级子公司B_利润表_2025-09.xlsx
+++ b/reports/一级子公司B_利润表_2025-09.xlsx
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>50443810</v>
+        <v>67212566</v>
       </c>
       <c r="G3" s="13" t="n"/>
       <c r="I3" s="5" t="n"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>0</v>
+        <v>14850519</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>0</v>
+        <v>129275891</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>0</v>
+        <v>211143</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>0</v>
+        <v>1823135</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>0</v>
+        <v>190134</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>0</v>
+        <v>1641205</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>0</v>
+        <v>158366</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>0</v>
+        <v>1367783</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>0</v>
+        <v>147592</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>0</v>
+        <v>1276492</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>0</v>
+        <v>84156</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>0</v>
+        <v>729254</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>0</v>
+        <v>62959</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>0</v>
+        <v>546752</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>50443810</v>
+        <v>66358216</v>
       </c>
       <c r="G11" s="13" t="n"/>
     </row>
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0</v>
+        <v>13996169</v>
       </c>
       <c r="G12" s="13" t="n"/>
     </row>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>0</v>
+        <v>8350547</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>0</v>
+        <v>72823732</v>
       </c>
     </row>
     <row r="14" ht="20.25" customHeight="1">
@@ -2408,10 +2408,10 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>0</v>
+        <v>1252636</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>0</v>
+        <v>10921904</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>0</v>
+        <v>626993</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>0</v>
+        <v>5461011</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>0</v>
+        <v>4187983</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>0</v>
+        <v>36412998</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>0</v>
+        <v>419813</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>0</v>
+        <v>3642400</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>0</v>
+        <v>315645</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>0</v>
+        <v>2732837</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>0</v>
+        <v>527195</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>0</v>
+        <v>4556502</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>0</v>
+        <v>422343</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>0</v>
+        <v>3646411</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>50363597</v>
+        <v>50702090</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>437260712</v>
+        <v>437663454</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -2672,10 +2672,10 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>80213</v>
+        <v>80428</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>720188</v>
+        <v>720706</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0</v>
+        <v>948566</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>0</v>
+        <v>8205834</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0</v>
+        <v>630963</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>0</v>
+        <v>5469187</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>46580534</v>
+        <v>59748312</v>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>26502672</v>
+        <v>33615578</v>
       </c>
       <c r="G26" s="13" t="n"/>
     </row>
@@ -2833,10 +2833,10 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>156708</v>
+        <v>7521582</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>1365681</v>
+        <v>65557296</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>26345964</v>
+        <v>26093996</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>227852681</v>
+        <v>227567595</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2899,10 +2899,10 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>1565930</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>0</v>
+        <v>13652266</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0</v>
+        <v>501701</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>0</v>
+        <v>4368869</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>314194</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>0</v>
+        <v>2731067</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>377959</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0</v>
+        <v>3278316</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0</v>
+        <v>284169</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>0</v>
+        <v>2459682</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0</v>
+        <v>189835</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>0</v>
+        <v>1640421</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -3097,10 +3097,10 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>158397</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>0</v>
+        <v>1367455</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -3130,10 +3130,10 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>1253286</v>
+        <v>1267521</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>10925112</v>
+        <v>10941778</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>42173</v>
+        <v>42218</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>364583</v>
+        <v>364740</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3196,10 +3196,10 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>2618619</v>
+        <v>2634203</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>22767827</v>
+        <v>22793404</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>15757474</v>
+        <v>15768902</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>136662776</v>
+        <v>136723875</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>0</v>
+        <v>2621544</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>0</v>
+        <v>22779053</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>448483</v>
+        <v>448379</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>4048620</v>
+        <v>4048420</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3328,10 +3328,10 @@
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>401931</v>
+        <v>397899</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>3601840</v>
+        <v>3597349</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>29828</v>
+        <v>29821</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>269832</v>
+        <v>269744</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0</v>
+        <v>134237</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>0</v>
+        <v>1213783</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0</v>
+        <v>274430</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>0</v>
+        <v>2389265</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3460,10 +3460,10 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0</v>
+        <v>89797</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>0</v>
+        <v>809519</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0</v>
+        <v>67515</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>0</v>
+        <v>607372</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0</v>
+        <v>112800</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>0</v>
+        <v>1012718</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>395576</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0</v>
+        <v>3417706</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3592,10 +3592,10 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0</v>
+        <v>60347</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>0</v>
+        <v>540475</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0</v>
+        <v>45267</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>0</v>
+        <v>405405</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0</v>
+        <v>75376</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>0</v>
+        <v>675641</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0</v>
+        <v>52669</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>0</v>
+        <v>472845</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0</v>
+        <v>37533</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>0</v>
+        <v>337629</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -3757,10 +3757,10 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0</v>
+        <v>29951</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>0</v>
+        <v>269993</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0</v>
+        <v>22413</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>0</v>
+        <v>202410</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>3863276</v>
+        <v>7565218</v>
       </c>
       <c r="G57" s="13" t="n"/>
     </row>
@@ -3854,7 +3854,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>-118668</v>
+        <v>4700141</v>
       </c>
       <c r="G58" s="13" t="n"/>
     </row>
@@ -3885,10 +3885,10 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0</v>
+        <v>156629</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>0</v>
+        <v>1365217</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3918,10 +3918,10 @@
         </is>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0</v>
+        <v>37346</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>0</v>
+        <v>337215</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3951,10 +3951,10 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>59684</v>
+        <v>59884</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>539695</v>
+        <v>539705</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3984,7 +3984,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>3803592</v>
+        <v>7661963</v>
       </c>
       <c r="G62" s="13" t="n"/>
     </row>
@@ -4015,10 +4015,10 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>1789371</v>
+        <v>1805338</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>16189301</v>
+        <v>16204370</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>2014221</v>
+        <v>5856625</v>
       </c>
       <c r="G64" s="13" t="n"/>
     </row>
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>2014221</v>
+        <v>5856625</v>
       </c>
       <c r="G66" s="13" t="n"/>
     </row>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>2014221</v>
+        <v>5856625</v>
       </c>
       <c r="G69" s="13" t="n"/>
     </row>
@@ -4410,7 +4410,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>2014221</v>
+        <v>5856625</v>
       </c>
       <c r="G76" s="13" t="n"/>
     </row>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>2014221</v>
+        <v>5856625</v>
       </c>
       <c r="G77" s="13" t="n"/>
     </row>
